--- a/product_selector_out/STM32L4R7-S7 - diff.xlsx
+++ b/product_selector_out/STM32L4R7-S7 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -43,21 +43,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C0C0C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B7E1CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -81,16 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +531,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +591,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +601,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +611,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="18">
@@ -667,22 +649,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -694,70 +672,62 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32L4S7VI</t>
+          <t>STM32L4S7ZI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1.71 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L4S7VI</t>
+          <t>STM32L4S7ZI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -766,21 +736,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L4S7VI</t>
+          <t>STM32L4R7AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -789,88 +759,76 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L4S7ZI</t>
+          <t>STM32L4R7AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L4S7ZI</t>
+          <t>STM32L4R7ZI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L4S7ZI</t>
+          <t>STM32L4R7ZI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1.71 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L4S7ZI</t>
+          <t>STM32L4R7VI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -884,7 +842,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -893,7 +851,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L4S7ZI</t>
+          <t>STM32L4R7VI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -907,7 +865,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -916,513 +874,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L4R7AI</t>
+          <t>STM32L4S7AI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L4R7AI</t>
+          <t>STM32L4S7AI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32L4R7AI</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1.71 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM32L4R7AI</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32L4R7AI</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM32L4R7ZI</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>STM32L4R7ZI</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>STM32L4R7ZI</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1.71 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STM32L4R7ZI</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>STM32L4R7ZI</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>STM32L4R7VI</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STM32L4R7VI</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>STM32L4R7VI</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1.71 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>STM32L4R7VI</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>STM32L4R7VI</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>STM32L4S7AI</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>STM32L4S7AI</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>STM32L4S7AI</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1.71 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>STM32L4S7AI</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>STM32L4S7AI</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E48"/>
+  <autoFilter ref="A18:E30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32L4R7-S7 - diff.xlsx
+++ b/product_selector_out/STM32L4R7-S7 - diff.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18">
